--- a/research/traditional_assets/database/data/nigeria/nigeria_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_retail_special_lines.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.00315955766192733</v>
+        <v>-0.1592178770949721</v>
       </c>
       <c r="H2">
-        <v>0.00315955766192733</v>
+        <v>-0.1675977653631285</v>
       </c>
       <c r="I2">
-        <v>-0.08372827804107424</v>
+        <v>-0.1564245810055866</v>
       </c>
       <c r="J2">
-        <v>-0.08372827804107424</v>
+        <v>-0.1564245810055866</v>
       </c>
       <c r="K2">
-        <v>-0.062</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.09794628751974724</v>
+        <v>-0.2346368715083799</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="V2">
-        <v>0.02542372881355932</v>
+        <v>0.04195804195804196</v>
+      </c>
+      <c r="W2">
+        <v>0.1948955916473318</v>
       </c>
       <c r="X2">
-        <v>0.3595997376687869</v>
+        <v>0.3755711001734854</v>
+      </c>
+      <c r="Y2">
+        <v>-0.1806755085261536</v>
+      </c>
+      <c r="Z2">
+        <v>8.731707317073173</v>
+      </c>
+      <c r="AA2">
+        <v>-1.365853658536586</v>
       </c>
       <c r="AB2">
-        <v>0.2082305258494513</v>
+        <v>0.1973919487874771</v>
+      </c>
+      <c r="AC2">
+        <v>-1.563245607324063</v>
       </c>
       <c r="AD2">
-        <v>0.481</v>
+        <v>0.248</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.481</v>
+        <v>0.248</v>
       </c>
       <c r="AG2">
-        <v>0.472</v>
+        <v>0.242</v>
       </c>
       <c r="AH2">
-        <v>0.5760479041916168</v>
+        <v>0.6342710997442454</v>
       </c>
       <c r="AI2">
-        <v>9.620000000000001</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="AJ2">
-        <v>0.5714285714285714</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="AK2">
-        <v>11.51219512195122</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="AL2">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AM2">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AN2">
-        <v>-53.44444444444445</v>
+        <v>-7.515151515151515</v>
       </c>
       <c r="AO2">
-        <v>-3.3125</v>
+        <v>-4</v>
       </c>
       <c r="AP2">
-        <v>-52.44444444444444</v>
+        <v>-7.333333333333333</v>
       </c>
       <c r="AQ2">
-        <v>-3.3125</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.00315955766192733</v>
+        <v>-0.1592178770949721</v>
       </c>
       <c r="H3">
-        <v>0.00315955766192733</v>
+        <v>-0.1675977653631285</v>
       </c>
       <c r="I3">
-        <v>-0.08372827804107424</v>
+        <v>-0.1564245810055866</v>
       </c>
       <c r="J3">
-        <v>-0.08372827804107424</v>
+        <v>-0.1564245810055866</v>
       </c>
       <c r="K3">
-        <v>-0.062</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.09794628751974724</v>
+        <v>-0.2346368715083799</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,58 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="V3">
-        <v>0.02542372881355932</v>
+        <v>0.04195804195804196</v>
+      </c>
+      <c r="W3">
+        <v>0.1948955916473318</v>
       </c>
       <c r="X3">
-        <v>0.3595997376687869</v>
+        <v>0.3755711001734854</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1806755085261536</v>
+      </c>
+      <c r="Z3">
+        <v>8.731707317073173</v>
+      </c>
+      <c r="AA3">
+        <v>-1.365853658536586</v>
       </c>
       <c r="AB3">
-        <v>0.2082305258494513</v>
+        <v>0.1973919487874771</v>
+      </c>
+      <c r="AC3">
+        <v>-1.563245607324063</v>
       </c>
       <c r="AD3">
-        <v>0.481</v>
+        <v>0.248</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.481</v>
+        <v>0.248</v>
       </c>
       <c r="AG3">
-        <v>0.472</v>
+        <v>0.242</v>
       </c>
       <c r="AH3">
-        <v>0.5760479041916168</v>
+        <v>0.6342710997442454</v>
       </c>
       <c r="AI3">
-        <v>9.620000000000001</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="AJ3">
-        <v>0.5714285714285714</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="AK3">
-        <v>11.51219512195122</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="AL3">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AM3">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AN3">
-        <v>-53.44444444444445</v>
+        <v>-7.515151515151515</v>
       </c>
       <c r="AO3">
-        <v>-3.3125</v>
+        <v>-4</v>
       </c>
       <c r="AP3">
-        <v>-52.44444444444444</v>
+        <v>-7.333333333333333</v>
       </c>
       <c r="AQ3">
-        <v>-3.3125</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
